--- a/AAII_Financials/Quarterly/TWOU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TWOU_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
   <si>
     <t>TWOU</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>255700</v>
+      </c>
+      <c r="E8" s="3">
         <v>229700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>222100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>238500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>236000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>232200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>241500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>253300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>243600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>232400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>237200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>232500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>215300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>201100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>182700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>175500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>163200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>153800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>135500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>122200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>115100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>107000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>97400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>92300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>86700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>70300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>65000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>64800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>57400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>52000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>97900</v>
+      </c>
+      <c r="E9" s="3">
         <v>109500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>111900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>114400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>117800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>111600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>114800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>123900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>119100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>107900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>112200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>109300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>106500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>102900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>93900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>86500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>84800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>82800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>63300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>46700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>43100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>39300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>38500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>33400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>31100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>27500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>24600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>20100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>19400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>157800</v>
+      </c>
+      <c r="E10" s="3">
         <v>120200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>110200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>124100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>118200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>120600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>126700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>129400</v>
-      </c>
-      <c r="K10" s="3">
-        <v>124500</v>
       </c>
       <c r="L10" s="3">
         <v>124500</v>
       </c>
       <c r="M10" s="3">
+        <v>124500</v>
+      </c>
+      <c r="N10" s="3">
         <v>125000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>123200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>108800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>98200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>88800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>89000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>78400</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>71000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>72200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>75500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>72000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>67700</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>58900</v>
       </c>
       <c r="Z10" s="3">
         <v>58900</v>
       </c>
       <c r="AA10" s="3">
+        <v>58900</v>
+      </c>
+      <c r="AB10" s="3">
         <v>55600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>42800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>40400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>44700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>38000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>33000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,64 +1298,67 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>76400</v>
+      </c>
+      <c r="E14" s="3">
         <v>14100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>137700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>21600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>91100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>16800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>58800</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>1100</v>
       </c>
-      <c r="N14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>11700</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>70400</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
@@ -1356,8 +1375,8 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1374,8 +1393,11 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1466,8 +1488,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>278200</v>
+      </c>
+      <c r="E17" s="3">
         <v>256600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>378200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>275500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>230600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>336500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>289400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>364700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>293300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>275900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>275400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>269600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>245300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>247000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>243400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>229400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>204500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>288800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>181500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>146700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>111800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>118800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>119400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>108300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>86700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>86000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>75800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>68500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>59700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>58800</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="E18" s="3">
         <v>-26900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-156100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-37000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-104300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-47900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-111400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-49700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-43500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-38200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-37100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-30000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-45900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-60700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-53900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-41300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-135000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-46000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-24500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>3300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-22000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-16000</v>
       </c>
-      <c r="AA18" s="3">
-        <v>0</v>
-      </c>
       <c r="AB18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="3">
         <v>-15700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,255 +1747,262 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>24400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>700</v>
       </c>
       <c r="Q20" s="3">
         <v>700</v>
       </c>
       <c r="R20" s="3">
+        <v>700</v>
+      </c>
+      <c r="S20" s="3">
         <v>-1800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>200</v>
       </c>
-      <c r="AB20" s="3">
-        <v>0</v>
-      </c>
       <c r="AC20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>200</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>100</v>
       </c>
-      <c r="AF20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E21" s="3">
         <v>1300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-128200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-6000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>39300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-76500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-17800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-77700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-18900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-17300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-12700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-4800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-21200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-36000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-32200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-17000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-112500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-29600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-12700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>14600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-1700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-14500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>6500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-9800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-8000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-4200</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E22" s="3">
         <v>19200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>18000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>15900</v>
-      </c>
-      <c r="I22" s="3">
-        <v>13900</v>
       </c>
       <c r="J22" s="3">
         <v>13900</v>
       </c>
       <c r="K22" s="3">
+        <v>13900</v>
+      </c>
+      <c r="L22" s="3">
         <v>18200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>16900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>8200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>7900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>6500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>5500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>2400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>100</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
@@ -1974,11 +2013,11 @@
         <v>0</v>
       </c>
       <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="3">
         <v>100</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
-      </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
@@ -1991,181 +2030,187 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-47300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-173400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-53900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-12300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-121700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-63000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-126000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-68000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-60400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-22000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-45600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-37600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-52700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-66500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-61200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-45500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-140400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-46700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-22500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-21900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-16100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-15700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-1100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-18700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1000</v>
       </c>
-      <c r="AC24" s="3">
-        <v>0</v>
-      </c>
       <c r="AD24" s="3">
         <v>0</v>
       </c>
@@ -2175,8 +2220,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-47400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-173700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-54100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-11800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-121700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-62900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-125800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-67300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-60100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-21800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-45600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-37700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-52600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-66200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-60100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-44600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-141100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-28000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-21600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-18300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-14900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-47400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-173700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-54100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-11800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-121700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-62900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-125800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-67300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-60100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-21800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-45600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-37700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-52600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-66200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-60100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-44600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-141100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-28000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-21600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-18300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-14900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
         <v>1200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-24400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-700</v>
       </c>
       <c r="Q32" s="3">
         <v>-700</v>
       </c>
       <c r="R32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="S32" s="3">
         <v>1800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-200</v>
       </c>
-      <c r="AB32" s="3">
-        <v>0</v>
-      </c>
       <c r="AC32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="3">
         <v>1000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-200</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-100</v>
       </c>
-      <c r="AF32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-47400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-173700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-54100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-11800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-121700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-62900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-125800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-67300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-60100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-21800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-45600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-37700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-52600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-66200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-60100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-44600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-141100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-28000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-21600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-18300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-14900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-47400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-173700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-54100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-11800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-121700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-62900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-125800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-67300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-60100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-21800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-45600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-37700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-52600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-66200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-60100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-44600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-141100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-28000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-21600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-18300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-14900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E41" s="3">
         <v>41100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>53300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>94200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>167500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>170200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>220800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>216600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>232900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>934300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>953100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>486800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>500600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>481300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>194800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>138200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>170600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>154100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>218700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>423600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>449800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>442200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>488800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>182100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>223400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>202400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>37400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>142900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>168700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>156900</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3507,13 +3596,13 @@
         <v>0</v>
       </c>
       <c r="W42" s="3">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="X42" s="3">
         <v>25000</v>
       </c>
-      <c r="Y42" s="3" t="s">
-        <v>8</v>
+      <c r="Y42" s="3">
+        <v>25000</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>8</v>
@@ -3527,8 +3616,8 @@
       <c r="AC42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD42" s="3">
-        <v>0</v>
+      <c r="AD42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE42" s="3">
         <v>0</v>
@@ -3536,100 +3625,106 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>144200</v>
+      </c>
+      <c r="E43" s="3">
         <v>142400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>117000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>104600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>96600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>128200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>100800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>107700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>96700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>95400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>101400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>74700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>46700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>95800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>71600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>75400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>33700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>84800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>71600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>70300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>32600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>49700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>50000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>40300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>14200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>42300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>23400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>28700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>7900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,221 +3815,230 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E45" s="3">
         <v>50400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>55500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>59200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>58200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>96500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>97400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>104400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>64200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>85400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>81100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>76000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>57600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>58500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>58600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>61400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>56700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>56000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>57900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>28300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>14300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>14900</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>15100</v>
       </c>
       <c r="Z45" s="3">
         <v>15100</v>
       </c>
       <c r="AA45" s="3">
+        <v>15100</v>
+      </c>
+      <c r="AB45" s="3">
         <v>10500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>13000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>109600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>9200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>8100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>251500</v>
+      </c>
+      <c r="E46" s="3">
         <v>234000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>225900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>258000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>322300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>394900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>419000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>428800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>393900</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1115100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1135600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>637600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>604900</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>635600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>325000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>275000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>260900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>294900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>348200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>522100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>521700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>531800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>554000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>237500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>248100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>257700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>170500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>180700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>184700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>185900</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E47" s="3">
         <v>18400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>16400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>14700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>14800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>21000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>21300</v>
       </c>
       <c r="J47" s="3">
         <v>21300</v>
       </c>
       <c r="K47" s="3">
+        <v>21300</v>
+      </c>
+      <c r="L47" s="3">
         <v>21600</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M47" s="3" t="s">
         <v>8</v>
@@ -3951,8 +4055,8 @@
       <c r="Q47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R47" s="3">
-        <v>0</v>
+      <c r="R47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S47" s="3">
         <v>0</v>
@@ -3978,17 +4082,17 @@
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-      <c r="AA47" s="3" t="s">
-        <v>8</v>
+      <c r="AA47" s="3">
+        <v>0</v>
       </c>
       <c r="AB47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AC47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD47" s="3">
         <v>2200</v>
-      </c>
-      <c r="AD47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE47" s="3" t="s">
         <v>8</v>
@@ -3996,192 +4100,201 @@
       <c r="AF47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>104200</v>
+      </c>
+      <c r="E48" s="3">
         <v>107700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>110200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>114200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>118200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>119700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>122000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>124700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>125500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>125900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>118200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>110400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>113500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>107100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>104900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>104700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>101000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>96500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>93900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>87200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>52300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>51500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>50300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>50700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>49100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>45000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>34400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>29700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>15600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1022700</v>
+      </c>
+      <c r="E49" s="3">
         <v>1098900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1116300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1265000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1284400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1302000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1399900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1429000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1500100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>705400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>718500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>721200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>728600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>724300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>726900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>729700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>751400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>750400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>828000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>206500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>198500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>193600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>190900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>190000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>162700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>152400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>37400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>34300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>31900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>68800</v>
+      </c>
+      <c r="E52" s="3">
         <v>79000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>69700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>73300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>71200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>72000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>71100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>69200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>68000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>87000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>77000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>86300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>97300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>85900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>75800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>72600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>73400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>71800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>61600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>48700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>34900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>34600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>30300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>26000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>22200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>21200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>17600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>16000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>12200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1459700</v>
+      </c>
+      <c r="E54" s="3">
         <v>1537900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1538400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1725200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1810900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1909600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>2033200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2072900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2109000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2033500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2049300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1555500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1544300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1552800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1232600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1182000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1186800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1213600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1331700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>864400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>807400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>811500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>825500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>504100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>482100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>476400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>262000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>260700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>244300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>234600</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,100 +4837,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E57" s="3">
         <v>54900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>48400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>39600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>46500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>57200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>28700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>59500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>50000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>41000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>31600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>43400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>22300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>27400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>34300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>38000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>65400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>59600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>66500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>48500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>27600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>34500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>32100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>31000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>22600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>32500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>4300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>3700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4892,376 +5025,391 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>213800</v>
+      </c>
+      <c r="E59" s="3">
         <v>259800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>247400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>274300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>232400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>325900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>375300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>332700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>283500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>259400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>260400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>231800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>215100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>219500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>178600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>165500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>90600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>105400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>92700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>53700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>40800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>49800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>64900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>51200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>35400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>41500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>47600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>40000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>37300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>33300</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>259300</v>
+      </c>
+      <c r="E60" s="3">
         <v>314600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>295800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>313900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>279000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>383100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>404000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>392200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>333500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>300400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>292000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>275200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>237400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>247000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>213000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>203500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>156000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>165000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>159100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>102200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>68500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>84300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>97000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>82100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>58000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>74000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>51900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>50800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>41100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>896500</v>
+      </c>
+      <c r="E61" s="3">
         <v>878100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>856400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>854300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>928600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>928200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>927700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>927300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>845300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>742800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>742100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>280400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>273200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>268200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>263100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>244600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>246600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>245900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>245500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>26900</v>
-      </c>
-      <c r="X61" s="3">
-        <v>28100</v>
       </c>
       <c r="Y61" s="3">
         <v>28100</v>
       </c>
       <c r="Z61" s="3">
+        <v>28100</v>
+      </c>
+      <c r="AA61" s="3">
         <v>27000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>26100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>21100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>18700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>13800</v>
       </c>
-      <c r="AE61" s="3">
-        <v>0</v>
-      </c>
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>84800</v>
+      </c>
+      <c r="E62" s="3">
         <v>88700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>92700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>97300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>101800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>104400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>95900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>100100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>101000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>110900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>97800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>89400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>92700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>86000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>77100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>77600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>73000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>69700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>66100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>64100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>6900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>7000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>6900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>9200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>10200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>11800</v>
-      </c>
-      <c r="AC62" s="3">
-        <v>300</v>
       </c>
       <c r="AD62" s="3">
         <v>300</v>
       </c>
       <c r="AE62" s="3">
+        <v>300</v>
+      </c>
+      <c r="AF62" s="3">
         <v>8000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1240600</v>
+      </c>
+      <c r="E66" s="3">
         <v>1281500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1244900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1265600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1309300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1415600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1427600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1419600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1279900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1154000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1131800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>645000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>603300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>601200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>553200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>525700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>475600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>480500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>470700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>169800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>102300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>119400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>132000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>118300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>94200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>106800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>70900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>64900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>49100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>41900</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1497600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1455100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1407700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1234000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1180000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1168100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1046500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-983600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-890600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-823400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-763300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-741400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-695900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-658200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-605700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-539500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-479400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-434800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-293700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-265700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-244200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-249000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-239100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-220700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-205800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-206300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-191600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-179900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-176300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-174100</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>219000</v>
+      </c>
+      <c r="E76" s="3">
         <v>256500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>293500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>459600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>501500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>493900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>605700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>653400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>829200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>879500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>917400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>910500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>941000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>951600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>679400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>656300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>711300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>733100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>861000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>694600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>705000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>692100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>693400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>385800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>387800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>369500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>191100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>195700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>195200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>192700</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-42400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-47400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-173700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-54100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-11800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-121700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-62900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-125800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-67300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-60100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-21800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-45600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-37700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-52600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-66200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-60100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-44600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-141100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-28000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-21600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-9900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-18300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-14900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E83" s="3">
         <v>29500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>27300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>33100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>29300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>31300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>34400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>30900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>26200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>26400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>25000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>25100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>23900</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>24000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>23500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>23200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>22300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>14700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>9700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>9400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>8600</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>7400</v>
       </c>
       <c r="Z83" s="3">
         <v>7400</v>
       </c>
       <c r="AA83" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AB83" s="3">
         <v>6300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>3800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>2700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-18700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-26300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>27500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>12400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-30100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>28700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-14900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>7600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>36500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>33700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-37700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-15400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-32500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>22900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-5800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-18800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>34200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>3500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-11600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>19600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-25900</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11600</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-15300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-18900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-20800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-19300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-18300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-6400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-7600</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-15300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-18900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-20900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-14300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-780900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-17400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>19900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-17000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-14900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-18300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-19100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-16400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-26700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-414200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>6000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-17400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-39800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-21600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-23700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-108200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-12000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-14300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-8400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7600</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,180 +8495,186 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E100" s="3">
         <v>18400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-2400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-89500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>94400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>456900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-6300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>301000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>70400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>2400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>239700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>2200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>331100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>190100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>5100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-1000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-600</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>2500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-2600</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-1600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-700</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>1300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-900</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>-700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-200</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>200</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC101" s="3" t="s">
-        <v>8</v>
+      <c r="AC101" s="3">
+        <v>0</v>
       </c>
       <c r="AD101" s="3" t="s">
         <v>8</v>
@@ -8437,96 +8685,102 @@
       <c r="AF101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-42600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-73300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-52600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>4200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-16300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-701400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-20000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>466300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>19300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>286500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>55500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-32400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>19000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-62700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-190100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-26200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>7500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-46600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>306700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-41300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>20900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>64000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-25800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>11800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-31300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/TWOU_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TWOU_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>TWOU</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>198400</v>
+      </c>
+      <c r="E8" s="3">
         <v>255700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>229700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>222100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>238500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>236000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>232200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>241500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>253300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>243600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>232400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>237200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>232500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>215300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>201100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>182700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>175500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>163200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>153800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>135500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>122200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>115100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>107000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>97400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>92300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>86700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>70300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>65000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>64800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>57400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>52000</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>91600</v>
+      </c>
+      <c r="E9" s="3">
         <v>97900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>109500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>111900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>114400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>117800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>111600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>114800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>123900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>119100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>107900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>112200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>109300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>106500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>102900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>93900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>86500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>84800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>82800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>63300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>46700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>43100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>39300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>38500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>33400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>31100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>27500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>24600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>20100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>19400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>19000</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>106800</v>
+      </c>
+      <c r="E10" s="3">
         <v>157800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>120200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>110200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>124100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>118200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>120600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>126700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>129400</v>
-      </c>
-      <c r="L10" s="3">
-        <v>124500</v>
       </c>
       <c r="M10" s="3">
         <v>124500</v>
       </c>
       <c r="N10" s="3">
+        <v>124500</v>
+      </c>
+      <c r="O10" s="3">
         <v>125000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>123200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>108800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>98200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>88800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>89000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>78400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>71000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>72200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>75500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>72000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>67700</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>58900</v>
       </c>
       <c r="AA10" s="3">
         <v>58900</v>
       </c>
       <c r="AB10" s="3">
+        <v>58900</v>
+      </c>
+      <c r="AC10" s="3">
         <v>55600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>42800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>40400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>44700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>38000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>33000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,67 +1318,70 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4700</v>
+      </c>
+      <c r="E14" s="3">
         <v>76400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>14100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>137700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>21600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>91100</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>16800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>58800</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>1100</v>
       </c>
-      <c r="O14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>11700</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>70400</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
@@ -1378,8 +1398,8 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1396,8 +1416,11 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1491,8 +1514,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>225700</v>
+      </c>
+      <c r="E17" s="3">
         <v>278200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>256600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>378200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>275500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>230600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>336500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>289400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>364700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>293300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>275900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>275400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>269600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>245300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>247000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>243400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>229400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>204500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>288800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>181500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>146700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>111800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>118800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>119400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>108300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>86700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>86000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>75800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>68500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>59700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>58800</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-27300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-22500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-26900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-156100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-37000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-104300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-47900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-111400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-49700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-43500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-38200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-37100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-45900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-60700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-53900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-41300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-135000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-46000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-24500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>3300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-11800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-22000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-16000</v>
       </c>
-      <c r="AB18" s="3">
-        <v>0</v>
-      </c>
       <c r="AC18" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="3">
         <v>-15700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-2300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,264 +1781,271 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-7800</v>
+      </c>
+      <c r="E20" s="3">
         <v>800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-1200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>24400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>700</v>
       </c>
       <c r="R20" s="3">
         <v>700</v>
       </c>
       <c r="S20" s="3">
+        <v>700</v>
+      </c>
+      <c r="T20" s="3">
         <v>-1800</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1900</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>200</v>
       </c>
-      <c r="AC20" s="3">
-        <v>0</v>
-      </c>
       <c r="AD20" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>100</v>
       </c>
-      <c r="AG20" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E21" s="3">
         <v>6800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-128200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-6000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>39300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-76500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-17800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-77700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-18900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-17300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-12700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-21200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-36000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-32200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-17000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-112500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-29600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-12700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>14600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-1700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-14500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>6500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-9800</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-8000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>-4200</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E22" s="3">
         <v>19500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>19200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>18500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>15900</v>
-      </c>
-      <c r="J22" s="3">
-        <v>13900</v>
       </c>
       <c r="K22" s="3">
         <v>13900</v>
       </c>
       <c r="L22" s="3">
+        <v>13900</v>
+      </c>
+      <c r="M22" s="3">
         <v>18200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>16900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>8200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>7600</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>6500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>5500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>5300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>5700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>2400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>100</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
-      </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
@@ -2016,11 +2056,11 @@
         <v>0</v>
       </c>
       <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="3">
         <v>100</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
-      </c>
       <c r="AD22" s="3">
         <v>0</v>
       </c>
@@ -2033,187 +2073,193 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-41200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-47300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-173400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-53900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-12300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-121700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-63000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-126000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-68000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-60400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-22000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-45600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-37600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-52700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-66500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-61200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-45500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-140400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-46700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-22500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-21900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-16100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-15700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-1100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-18700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1000</v>
       </c>
-      <c r="AD24" s="3">
-        <v>0</v>
-      </c>
       <c r="AE24" s="3">
         <v>0</v>
       </c>
@@ -2223,8 +2269,11 @@
       <c r="AG24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-54600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-42400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-47400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-173700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-54100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-11800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-121700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-62900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-125800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-67300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-60100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-45600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-37700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-52600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-66200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-60100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-44600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-141100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-28000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-21600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-18300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-14900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-14700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-54600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-42400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-47400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-173700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-54100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-11800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-121700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-62900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-125800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-67300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-60100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-21800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-45600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-37700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-52600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-66200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-60100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-44600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-141100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-28000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-21600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-18300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-14900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-14700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E32" s="3">
         <v>-800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>1200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-24400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-700</v>
       </c>
       <c r="R32" s="3">
         <v>-700</v>
       </c>
       <c r="S32" s="3">
+        <v>-700</v>
+      </c>
+      <c r="T32" s="3">
         <v>1800</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-200</v>
       </c>
-      <c r="AC32" s="3">
-        <v>0</v>
-      </c>
       <c r="AD32" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="3">
         <v>1000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-100</v>
       </c>
-      <c r="AG32" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-54600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-42400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-47400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-173700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-54100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-11800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-121700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-62900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-125800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-67300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-60100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-21800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-45600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-37700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-52600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-66200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-60100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-44600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-141100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-28000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-21600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-18300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-14900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-14700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-54600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-42400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-47400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-173700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-54100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-11800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-121700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-62900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-125800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-67300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-60100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-21800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-45600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-37700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-52600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-66200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-60100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-44600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-141100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-28000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-21600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-18300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-14900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-14700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>124700</v>
+      </c>
+      <c r="E41" s="3">
         <v>60700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>41100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>53300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>94200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>167500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>170200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>220800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>216600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>232900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>934300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>953100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>486800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>500600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>481300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>194800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>138200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>170600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>154100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>218700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>423600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>449800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>442200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>488800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>182100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>223400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>202400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>37400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>142900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>168700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>156900</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3599,13 +3689,13 @@
         <v>0</v>
       </c>
       <c r="X42" s="3">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="Y42" s="3">
         <v>25000</v>
       </c>
-      <c r="Z42" s="3" t="s">
-        <v>8</v>
+      <c r="Z42" s="3">
+        <v>25000</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>8</v>
@@ -3619,8 +3709,8 @@
       <c r="AD42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
+      <c r="AE42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF42" s="3">
         <v>0</v>
@@ -3628,103 +3718,109 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>91400</v>
+      </c>
+      <c r="E43" s="3">
         <v>144200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>142400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>117000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>104600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>96600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>128200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>107700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>96700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>95400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>101400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>74700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>46700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>95800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>71600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>75400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>33700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>84800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>71600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>70300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>32600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>49700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>50000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>40300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>14200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>42300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>23400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>28700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>7900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>21000</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,230 +3914,239 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E45" s="3">
         <v>46500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>50400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>55500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>59200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>58200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>96500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>97400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>104400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>64200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>85400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>81100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>76000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>57600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>58500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>58600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>61400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>56700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>56000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>57900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>28300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>14300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>14900</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>15100</v>
       </c>
       <c r="AA45" s="3">
         <v>15100</v>
       </c>
       <c r="AB45" s="3">
+        <v>15100</v>
+      </c>
+      <c r="AC45" s="3">
         <v>10500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>13000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>109600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>9200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>8100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>259400</v>
+      </c>
+      <c r="E46" s="3">
         <v>251500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>234000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>225900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>258000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>322300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>394900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>419000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>428800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>393900</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1115100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1135600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>637600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>604900</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>635600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>325000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>275000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>260900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>294900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>348200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>522100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>521700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>531800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>554000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>237500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>248100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>257700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>170500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>180700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>184700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>185900</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E47" s="3">
         <v>12500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>18400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>16400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>14700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>14800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>21000</v>
-      </c>
-      <c r="J47" s="3">
-        <v>21300</v>
       </c>
       <c r="K47" s="3">
         <v>21300</v>
       </c>
       <c r="L47" s="3">
+        <v>21300</v>
+      </c>
+      <c r="M47" s="3">
         <v>21600</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N47" s="3" t="s">
         <v>8</v>
@@ -4058,8 +4163,8 @@
       <c r="R47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S47" s="3">
-        <v>0</v>
+      <c r="S47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T47" s="3">
         <v>0</v>
@@ -4085,17 +4190,17 @@
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-      <c r="AB47" s="3" t="s">
-        <v>8</v>
+      <c r="AB47" s="3">
+        <v>0</v>
       </c>
       <c r="AC47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AD47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE47" s="3">
         <v>2200</v>
-      </c>
-      <c r="AE47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF47" s="3" t="s">
         <v>8</v>
@@ -4103,198 +4208,207 @@
       <c r="AG47" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>99800</v>
+      </c>
+      <c r="E48" s="3">
         <v>104200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>107700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>110200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>114200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>118200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>119700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>122000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>124700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>125500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>125900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>118200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>110400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>113500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>107100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>104900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>104700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>101000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>96500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>93900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>87200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>52300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>51500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>50300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>50700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>49100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>45000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>34400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>29700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>15600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1007100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1022700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1098900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1116300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1265000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1284400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1302000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1399900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1429000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1500100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>705400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>718500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>721200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>728600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>724300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>726900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>729700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>751400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>750400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>828000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>206500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>198500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>193600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>190900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>190000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>162700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>152400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>37400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>34300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>31900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>29400</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>51700</v>
+      </c>
+      <c r="E52" s="3">
         <v>68800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>79000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>69700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>73300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>71200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>72000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>71100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>69200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>68000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>87000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>77000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>86300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>97300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>85900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>75800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>72600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>73400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>71800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>61600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>48700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>34900</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>34600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>30300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>26000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>22200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>21200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>17600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>16000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>12200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1432900</v>
+      </c>
+      <c r="E54" s="3">
         <v>1459700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1537900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1538400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1725200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1810900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1909600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>2033200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>2072900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>2109000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>2033500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>2049300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1555500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1544300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1552800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1232600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1182000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1186800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1213600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1331700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>864400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>807400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>811500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>825500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>504100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>482100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>476400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>262000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>260700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>244300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>234600</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,8 +4968,9 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -4847,94 +4978,97 @@
         <v>45500</v>
       </c>
       <c r="E57" s="3">
+        <v>45500</v>
+      </c>
+      <c r="F57" s="3">
         <v>54900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>48400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>39600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>46500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>57200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>28700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>59500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>50000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>41000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>31600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>43400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>22300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>27400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>34300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>38000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>65400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>59600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>66500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>48500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>27600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>34500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>32100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>31000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>22600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>32500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>4300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>4800</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5028,388 +5162,403 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>239300</v>
+      </c>
+      <c r="E59" s="3">
         <v>213800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>259800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>247400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>274300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>232400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>325900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>375300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>332700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>283500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>259400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>260400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>231800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>215100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>219500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>178600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>165500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>90600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>105400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>92700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>53700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>40800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>49800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>64900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>51200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>35400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>41500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>47600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>40000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>37300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>33300</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>284800</v>
+      </c>
+      <c r="E60" s="3">
         <v>259300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>314600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>295800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>313900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>279000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>383100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>404000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>392200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>333500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>300400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>292000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>275200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>237400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>247000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>213000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>203500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>156000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>165000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>159100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>102200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>68500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>84300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>97000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>82100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>58000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>74000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>51900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>50800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>41100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>38000</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>898400</v>
+      </c>
+      <c r="E61" s="3">
         <v>896500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>878100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>856400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>854300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>928600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>928200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>927700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>927300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>845300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>742800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>742100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>280400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>273200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>268200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>263100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>244600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>246600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>245900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>245500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>3500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>26900</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>28100</v>
       </c>
       <c r="Z61" s="3">
         <v>28100</v>
       </c>
       <c r="AA61" s="3">
+        <v>28100</v>
+      </c>
+      <c r="AB61" s="3">
         <v>27000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>26100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>21100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>18700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>13800</v>
       </c>
-      <c r="AF61" s="3">
-        <v>0</v>
-      </c>
       <c r="AG61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>81200</v>
+      </c>
+      <c r="E62" s="3">
         <v>84800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>88700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>92700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>97300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>101800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>104400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>95900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>100100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>101000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>110900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>97800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>89400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>92700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>86000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>77100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>77600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>73000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>69700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>66100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>64100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>6900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>7000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>6900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>9200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>10200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>11800</v>
-      </c>
-      <c r="AD62" s="3">
-        <v>300</v>
       </c>
       <c r="AE62" s="3">
         <v>300</v>
       </c>
       <c r="AF62" s="3">
+        <v>300</v>
+      </c>
+      <c r="AG62" s="3">
         <v>8000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>3900</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1264400</v>
+      </c>
+      <c r="E66" s="3">
         <v>1240600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1281500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1244900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1265600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1309300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1415600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1427600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1419600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1279900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1154000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1131800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>645000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>603300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>601200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>553200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>525700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>475600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>480500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>470700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>169800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>102300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>119400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>132000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>118300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>94200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>106800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>70900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>64900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>49100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>41900</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1552200</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1497600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1455100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1407700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1234000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1180000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1168100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-1046500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-983600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-890600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-823400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-763300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-741400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-695900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-658200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-605700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-539500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-479400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-434800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-293700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-265700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-244200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-249000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-239100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-220700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-205800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-206300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-191600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-179900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-176300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-174100</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>168600</v>
+      </c>
+      <c r="E76" s="3">
         <v>219000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>256500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>293500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>459600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>501500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>493900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>605700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>653400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>829200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>879500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>917400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>910500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>941000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>951600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>679400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>656300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>711300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>733100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>861000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>694600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>705000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>692100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>693400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>385800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>387800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>369500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>191100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>195700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>195200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>192700</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-54600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-42400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-47400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-173700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-54100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-11800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-121700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-62900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-125800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-67300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-60100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-21800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-45600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-37700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-52600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-66200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-60100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-44600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-141100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-28000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-21600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-9900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-18300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-14900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-14700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-11800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-6800</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E83" s="3">
         <v>28500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>29500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>27300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>30000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>33100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>29300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>31300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>34400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>30900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>26200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>26400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>25000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>25100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>23900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>24000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>23500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>23200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>22300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>14700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>9700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>9400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>8600</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>7400</v>
       </c>
       <c r="AA83" s="3">
         <v>7400</v>
       </c>
       <c r="AB83" s="3">
+        <v>7400</v>
+      </c>
+      <c r="AC83" s="3">
         <v>6300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>3800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>3600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>2700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>72200</v>
+      </c>
+      <c r="E89" s="3">
         <v>14100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-18700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-26300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>27500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-30100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>28700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-14900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>7600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>36500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>3200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-9900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>33700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-37700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-15400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-32500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>22900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-5800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-18800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>34200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-17900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>3500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-11600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>19600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-25900</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-15300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-18900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-19300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-19800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-18300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-1800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-2100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-6400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-5500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-6100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-8400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-7600</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-13200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-15300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-18900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-20900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-780900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-17400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>19900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-14900</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-18300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-19100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-16400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-26700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-414200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>6000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-17400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-39800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-21600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-23700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-108200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-12000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-14300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-8400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-7600</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,186 +8741,192 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E100" s="3">
         <v>18500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>18400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-89500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>94400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>456900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-6300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>301000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>70400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-2500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>2400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>239700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>2200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>331100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>190100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>5100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>2200</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E101" s="3">
         <v>200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-1000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>2500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-2600</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>-1600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-700</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>1300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>200</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-900</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
-      </c>
       <c r="U101" s="3">
+        <v>0</v>
+      </c>
+      <c r="V101" s="3">
         <v>-700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-200</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>200</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD101" s="3" t="s">
-        <v>8</v>
+      <c r="AD101" s="3">
+        <v>0</v>
       </c>
       <c r="AE101" s="3" t="s">
         <v>8</v>
@@ -8688,99 +8937,105 @@
       <c r="AG101" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E102" s="3">
         <v>19500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-42600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-73300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-52600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>4200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-16300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-701400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-20000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>466300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-13800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>19300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>286500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>55500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-32400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>19000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-62700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-190100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-26200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>7500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-46600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>306700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-41300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>20900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>64000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-25800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>11800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-31300</v>
       </c>
     </row>
